--- a/premise/data/additional_inventories/lci-lithium.xlsx
+++ b/premise/data/additional_inventories/lci-lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F05B59A-3BC4-5940-BAD1-0A6C6F6C687C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C995736C-4528-6444-9125-4E59C7A7F0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" tabRatio="847" activeTab="6" xr2:uid="{EF7E5FDC-15C0-45A1-93C9-9ABA15D611A1}"/>
+    <workbookView xWindow="32700" yWindow="180" windowWidth="29040" windowHeight="17520" tabRatio="847" activeTab="4" xr2:uid="{EF7E5FDC-15C0-45A1-93C9-9ABA15D611A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LCI - Salar de Cauchari-Olaroz'!$A$1:$M$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'LCI - Salar de Olaroz'!$A$1:$M$88</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="158">
   <si>
     <t>database</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>CN</t>
+  </si>
+  <si>
+    <t>electricity, high voltage, production mix</t>
+  </si>
+  <si>
+    <t>CN-QH</t>
   </si>
   <si>
     <t>Olaroz_38</t>
@@ -525,9 +531,6 @@
   </si>
   <si>
     <t>market for neutralising agent, sodium hydroxide-equivalent</t>
-  </si>
-  <si>
-    <t>market group for electricity, high voltage</t>
   </si>
 </sst>
 </file>
@@ -537,7 +540,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,13 +572,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -603,14 +599,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,37 +933,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1000,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -1008,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1037,10 +1032,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1074,10 +1069,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
@@ -1097,10 +1092,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -1121,10 +1116,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
         <v>54</v>
@@ -1145,10 +1140,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
         <v>54</v>
@@ -1169,10 +1164,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
         <v>54</v>
@@ -1193,10 +1188,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -1217,10 +1212,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
         <v>45</v>
@@ -1233,7 +1228,7 @@
         <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G18" t="s">
         <v>27</v>
@@ -1244,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1252,7 +1247,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1281,10 +1276,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1318,10 +1313,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -1341,10 +1336,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
@@ -1356,7 +1351,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G29" t="s">
         <v>27</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -1380,7 +1375,7 @@
         <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G30" t="s">
         <v>27</v>
@@ -1415,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -1423,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -1452,10 +1447,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -1593,7 +1588,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -1631,10 +1626,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -1774,7 +1769,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
@@ -1782,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
@@ -1811,10 +1806,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
@@ -1865,10 +1860,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -1923,7 +1918,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -1931,7 +1926,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
@@ -1960,10 +1955,10 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
@@ -2014,10 +2009,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -2136,10 +2131,10 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -2293,7 +2288,7 @@
         <v>2</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
@@ -2301,7 +2296,7 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
@@ -2330,10 +2325,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
@@ -2384,10 +2379,10 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -2407,10 +2402,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -2512,10 +2507,10 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
         <v>45</v>
@@ -2547,7 +2542,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B67" t="s">
         <v>46</v>
@@ -2582,10 +2577,10 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -2620,7 +2615,7 @@
         <v>2</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
@@ -2628,7 +2623,7 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
@@ -2657,10 +2652,10 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
@@ -2711,10 +2706,10 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -2773,10 +2768,10 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -2880,10 +2875,10 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -2906,7 +2901,7 @@
         <v>2</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
@@ -2914,7 +2909,7 @@
         <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
@@ -2943,10 +2938,10 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
@@ -2997,10 +2992,10 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -3020,10 +3015,10 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
@@ -3127,10 +3122,10 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
@@ -3165,7 +3160,7 @@
         <v>2</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
@@ -3173,7 +3168,7 @@
         <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
@@ -3202,10 +3197,10 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
@@ -3256,10 +3251,10 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
@@ -3314,10 +3309,10 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -3423,10 +3418,10 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C112" t="s">
         <v>5</v>
@@ -3461,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
@@ -3469,7 +3464,7 @@
         <v>3</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
@@ -3498,10 +3493,10 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B119" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
@@ -3552,10 +3547,10 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B122" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3610,10 +3605,10 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B124" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -3649,10 +3644,10 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B125" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C125" t="s">
         <v>5</v>
@@ -3719,7 +3714,7 @@
         <v>2</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
@@ -3727,7 +3722,7 @@
         <v>3</v>
       </c>
       <c r="B129" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.2">
@@ -3756,10 +3751,10 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B133" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
@@ -3810,10 +3805,10 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" t="s">
         <v>103</v>
-      </c>
-      <c r="B136" t="s">
-        <v>101</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -3833,10 +3828,10 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B137" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
@@ -3872,10 +3867,10 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B138" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
@@ -3949,7 +3944,7 @@
         <v>2</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.2">
@@ -3957,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="B142" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.2">
@@ -3986,10 +3981,10 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B146" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.2">
@@ -4040,10 +4035,10 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B149" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
@@ -4098,10 +4093,10 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
+        <v>105</v>
+      </c>
+      <c r="B151" t="s">
         <v>103</v>
-      </c>
-      <c r="B151" t="s">
-        <v>101</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
@@ -4262,7 +4257,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -4270,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -4299,10 +4294,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -4353,10 +4348,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
@@ -4440,7 +4435,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -4448,7 +4443,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -4477,10 +4472,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -4531,10 +4526,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
         <v>54</v>
@@ -4546,7 +4541,7 @@
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
         <v>18</v>
@@ -4691,10 +4686,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
         <v>54</v>
@@ -4706,7 +4701,7 @@
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G26" t="s">
         <v>27</v>
@@ -4813,7 +4808,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
@@ -4821,7 +4816,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -4850,10 +4845,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -4904,10 +4899,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
         <v>54</v>
@@ -4919,7 +4914,7 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -4930,10 +4925,10 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
         <v>54</v>
@@ -4945,7 +4940,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G40" t="s">
         <v>27</v>
@@ -5069,10 +5064,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
         <v>54</v>
@@ -5084,7 +5079,7 @@
         <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
@@ -5107,7 +5102,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
@@ -5115,7 +5110,7 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
@@ -5144,10 +5139,10 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
@@ -5198,10 +5193,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s">
         <v>54</v>
@@ -5213,7 +5208,7 @@
         <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G54" t="s">
         <v>18</v>
@@ -5256,10 +5251,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s">
         <v>54</v>
@@ -5271,7 +5266,7 @@
         <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G56" t="s">
         <v>27</v>
@@ -5361,10 +5356,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
         <v>54</v>
@@ -5376,7 +5371,7 @@
         <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G59" t="s">
         <v>27</v>
@@ -5451,10 +5446,10 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
         <v>54</v>
@@ -5466,7 +5461,7 @@
         <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -5497,10 +5492,10 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C64" t="s">
         <v>45</v>
@@ -5520,7 +5515,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D65">
         <v>1.1780852612682483E-2</v>
@@ -5535,12 +5530,12 @@
         <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D66">
         <v>1.6725901857512168E-3</v>
@@ -5555,12 +5550,12 @@
         <v>21</v>
       </c>
       <c r="H66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D67">
         <v>5.0904918696776183E-4</v>
@@ -5575,7 +5570,7 @@
         <v>21</v>
       </c>
       <c r="H67" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5583,7 +5578,7 @@
         <v>2</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -5591,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -5620,10 +5615,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -5659,10 +5654,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C77" t="s">
         <v>54</v>
@@ -5674,7 +5669,7 @@
         <v>17</v>
       </c>
       <c r="F77" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G77" t="s">
         <v>18</v>
@@ -5682,10 +5677,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C78" t="s">
         <v>54</v>
@@ -5698,7 +5693,7 @@
         <v>17</v>
       </c>
       <c r="F78" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G78" t="s">
         <v>27</v>
@@ -5730,10 +5725,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C80" t="s">
         <v>54</v>
@@ -5746,7 +5741,7 @@
         <v>17</v>
       </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G80" t="s">
         <v>27</v>
@@ -5874,7 +5869,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -5882,7 +5877,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -5911,10 +5906,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -5965,10 +5960,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
@@ -5980,7 +5975,7 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
@@ -6122,10 +6117,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
         <v>54</v>
@@ -6137,7 +6132,7 @@
         <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
@@ -6244,7 +6239,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -6252,7 +6247,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -6281,10 +6276,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -6335,10 +6330,10 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
@@ -6350,7 +6345,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G27" t="s">
         <v>18</v>
@@ -6358,10 +6353,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
         <v>54</v>
@@ -6373,7 +6368,7 @@
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6428,10 +6423,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -6443,7 +6438,7 @@
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
         <v>27</v>
@@ -6463,7 +6458,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
@@ -6498,10 +6493,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
         <v>54</v>
@@ -6513,7 +6508,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
         <v>27</v>
@@ -6536,7 +6531,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -6544,7 +6539,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -6573,10 +6568,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
@@ -6627,10 +6622,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
         <v>54</v>
@@ -6642,7 +6637,7 @@
         <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G42" t="s">
         <v>18</v>
@@ -6650,10 +6645,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>54</v>
@@ -6665,7 +6660,7 @@
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G43" t="s">
         <v>27</v>
@@ -6743,10 +6738,10 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
         <v>54</v>
@@ -6758,7 +6753,7 @@
         <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G46" t="s">
         <v>27</v>
@@ -6781,7 +6776,7 @@
         <v>2</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -6789,7 +6784,7 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
@@ -6818,10 +6813,10 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
@@ -6872,10 +6867,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
         <v>54</v>
@@ -6887,7 +6882,7 @@
         <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G56" t="s">
         <v>18</v>
@@ -6927,10 +6922,10 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s">
         <v>54</v>
@@ -6942,7 +6937,7 @@
         <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G58" t="s">
         <v>27</v>
@@ -6997,10 +6992,10 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
         <v>54</v>
@@ -7012,7 +7007,7 @@
         <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -7035,7 +7030,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
@@ -7043,7 +7038,7 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
@@ -7072,10 +7067,10 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
@@ -7126,10 +7121,10 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
         <v>54</v>
@@ -7141,7 +7136,7 @@
         <v>17</v>
       </c>
       <c r="F70" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G70" t="s">
         <v>18</v>
@@ -7181,10 +7176,10 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C72" t="s">
         <v>54</v>
@@ -7196,7 +7191,7 @@
         <v>17</v>
       </c>
       <c r="F72" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G72" t="s">
         <v>27</v>
@@ -7216,10 +7211,10 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
         <v>37</v>
@@ -7251,10 +7246,10 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C74" t="s">
         <v>54</v>
@@ -7266,7 +7261,7 @@
         <v>17</v>
       </c>
       <c r="F74" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G74" t="s">
         <v>27</v>
@@ -7289,7 +7284,7 @@
         <v>2</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
@@ -7297,7 +7292,7 @@
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
@@ -7326,10 +7321,10 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
@@ -7380,10 +7375,10 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C84" t="s">
         <v>54</v>
@@ -7395,7 +7390,7 @@
         <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G84" t="s">
         <v>18</v>
@@ -7403,10 +7398,10 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B85" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C85" t="s">
         <v>54</v>
@@ -7418,7 +7413,7 @@
         <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G85" t="s">
         <v>27</v>
@@ -7502,10 +7497,10 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B88" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C88" t="s">
         <v>45</v>
@@ -7668,10 +7663,10 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C93" t="s">
         <v>54</v>
@@ -7683,7 +7678,7 @@
         <v>17</v>
       </c>
       <c r="F93" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G93" t="s">
         <v>27</v>
@@ -7703,7 +7698,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D94">
         <v>3.7950677799495399E-3</v>
@@ -7718,7 +7713,7 @@
         <v>21</v>
       </c>
       <c r="H94" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I94">
         <v>2</v>
@@ -7744,7 +7739,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D95">
         <v>5.3880591937555198E-4</v>
@@ -7759,7 +7754,7 @@
         <v>21</v>
       </c>
       <c r="H95" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I95">
         <v>2</v>
@@ -7785,7 +7780,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D96">
         <v>1.6398441024473301E-4</v>
@@ -7800,7 +7795,7 @@
         <v>21</v>
       </c>
       <c r="H96" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I96">
         <v>2</v>
@@ -7829,7 +7824,7 @@
         <v>2</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
@@ -7837,7 +7832,7 @@
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
@@ -7866,10 +7861,10 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B103" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
@@ -7920,10 +7915,10 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C106" t="s">
         <v>54</v>
@@ -7935,7 +7930,7 @@
         <v>17</v>
       </c>
       <c r="F106" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G106" t="s">
         <v>18</v>
@@ -7943,10 +7938,10 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
         <v>54</v>
@@ -7958,7 +7953,7 @@
         <v>17</v>
       </c>
       <c r="F107" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G107" t="s">
         <v>27</v>
@@ -8010,10 +8005,10 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C109" t="s">
         <v>54</v>
@@ -8025,7 +8020,7 @@
         <v>17</v>
       </c>
       <c r="F109" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G109" t="s">
         <v>27</v>
@@ -8106,7 +8101,7 @@
         <v>2</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
@@ -8114,7 +8109,7 @@
         <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
@@ -8143,10 +8138,10 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
@@ -8197,10 +8192,10 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C121" t="s">
         <v>54</v>
@@ -8212,7 +8207,7 @@
         <v>17</v>
       </c>
       <c r="F121" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G121" t="s">
         <v>18</v>
@@ -8220,10 +8215,10 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C122" t="s">
         <v>54</v>
@@ -8235,7 +8230,7 @@
         <v>17</v>
       </c>
       <c r="F122" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -8287,10 +8282,10 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C124" t="s">
         <v>54</v>
@@ -8302,7 +8297,7 @@
         <v>17</v>
       </c>
       <c r="F124" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G124" t="s">
         <v>27</v>
@@ -8479,7 +8474,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -8487,7 +8482,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -8516,10 +8511,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -8570,10 +8565,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
@@ -8585,7 +8580,7 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
@@ -8727,10 +8722,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
         <v>54</v>
@@ -8742,7 +8737,7 @@
         <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
@@ -8849,7 +8844,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -8857,7 +8852,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -8886,10 +8881,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -8940,10 +8935,10 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
@@ -8955,7 +8950,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
         <v>18</v>
@@ -8995,10 +8990,10 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
         <v>54</v>
@@ -9010,7 +9005,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G29" t="s">
         <v>27</v>
@@ -9088,10 +9083,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -9103,7 +9098,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
         <v>27</v>
@@ -9123,7 +9118,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -9158,10 +9153,10 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
         <v>54</v>
@@ -9173,7 +9168,7 @@
         <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
         <v>27</v>
@@ -9196,7 +9191,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -9204,7 +9199,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
@@ -9233,10 +9228,10 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
@@ -9287,10 +9282,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
         <v>54</v>
@@ -9302,7 +9297,7 @@
         <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G44" t="s">
         <v>18</v>
@@ -9310,10 +9305,10 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
         <v>54</v>
@@ -9325,7 +9320,7 @@
         <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
         <v>27</v>
@@ -9447,10 +9442,10 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
         <v>54</v>
@@ -9462,7 +9457,7 @@
         <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G49" t="s">
         <v>27</v>
@@ -9485,7 +9480,7 @@
         <v>2</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
@@ -9493,7 +9488,7 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
@@ -9522,10 +9517,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
@@ -9576,10 +9571,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C59" t="s">
         <v>54</v>
@@ -9591,7 +9586,7 @@
         <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G59" t="s">
         <v>18</v>
@@ -9631,10 +9626,10 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
         <v>54</v>
@@ -9646,7 +9641,7 @@
         <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -9724,10 +9719,10 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
         <v>54</v>
@@ -9739,7 +9734,7 @@
         <v>17</v>
       </c>
       <c r="F64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G64" t="s">
         <v>27</v>
@@ -9762,7 +9757,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
@@ -9770,7 +9765,7 @@
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
@@ -9799,10 +9794,10 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
@@ -9853,10 +9848,10 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C74" t="s">
         <v>54</v>
@@ -9868,7 +9863,7 @@
         <v>17</v>
       </c>
       <c r="F74" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G74" t="s">
         <v>18</v>
@@ -9876,10 +9871,10 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B75" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C75" t="s">
         <v>54</v>
@@ -9891,7 +9886,7 @@
         <v>17</v>
       </c>
       <c r="F75" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G75" t="s">
         <v>27</v>
@@ -9943,10 +9938,10 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C77" t="s">
         <v>54</v>
@@ -9958,7 +9953,7 @@
         <v>17</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
@@ -10010,10 +10005,10 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C79" t="s">
         <v>54</v>
@@ -10025,7 +10020,7 @@
         <v>17</v>
       </c>
       <c r="F79" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G79" t="s">
         <v>27</v>
@@ -10083,7 +10078,7 @@
         <v>2</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
@@ -10091,7 +10086,7 @@
         <v>3</v>
       </c>
       <c r="B83" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
@@ -10120,10 +10115,10 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
@@ -10174,10 +10169,10 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B90" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C90" t="s">
         <v>54</v>
@@ -10189,7 +10184,7 @@
         <v>17</v>
       </c>
       <c r="F90" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G90" t="s">
         <v>18</v>
@@ -10197,10 +10192,10 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
         <v>54</v>
@@ -10212,7 +10207,7 @@
         <v>17</v>
       </c>
       <c r="F91" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G91" t="s">
         <v>27</v>
@@ -10264,10 +10259,10 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C93" t="s">
         <v>54</v>
@@ -10279,7 +10274,7 @@
         <v>17</v>
       </c>
       <c r="F93" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G93" t="s">
         <v>27</v>
@@ -10454,7 +10449,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -10462,7 +10457,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -10491,10 +10486,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -10545,10 +10540,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>58</v>
@@ -10568,13 +10563,13 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10">
         <v>3.6029999999999999E-3</v>
@@ -10632,7 +10627,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -10640,7 +10635,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -10669,10 +10664,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -10723,10 +10718,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
         <v>58</v>
@@ -10738,7 +10733,7 @@
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
         <v>18</v>
@@ -10775,13 +10770,13 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23">
         <v>5.2450354690000006E-3</v>
@@ -10839,10 +10834,10 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
         <v>58</v>
@@ -10854,7 +10849,7 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
@@ -10871,10 +10866,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
         <v>45</v>
@@ -10906,7 +10901,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
@@ -10914,7 +10909,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
@@ -10943,10 +10938,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -10997,10 +10992,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
         <v>58</v>
@@ -11012,7 +11007,7 @@
         <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s">
         <v>18</v>
@@ -11020,10 +11015,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
@@ -11035,7 +11030,7 @@
         <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G37" t="s">
         <v>27</v>
@@ -11083,14 +11078,14 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>156</v>
+      <c r="A39" t="s">
+        <v>59</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D39">
         <v>8.0888266046705761E-3</v>
@@ -11116,10 +11111,10 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
         <v>58</v>
@@ -11131,7 +11126,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G40" t="s">
         <v>27</v>
@@ -11174,10 +11169,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
@@ -11206,7 +11201,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D43">
         <v>4.7150161860281198E-3</v>
@@ -11221,7 +11216,7 @@
         <v>21</v>
       </c>
       <c r="H43" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I43">
         <v>2</v>
@@ -11247,7 +11242,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D44">
         <v>6.6941587826325197E-4</v>
@@ -11262,7 +11257,7 @@
         <v>21</v>
       </c>
       <c r="H44" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I44">
         <v>2</v>
@@ -11288,7 +11283,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D45">
         <v>2.03735267297511E-4</v>
@@ -11303,7 +11298,7 @@
         <v>21</v>
       </c>
       <c r="H45" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I45">
         <v>2</v>
@@ -11332,7 +11327,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
@@ -11340,7 +11335,7 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -11369,10 +11364,10 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
@@ -11423,10 +11418,10 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
         <v>58</v>
@@ -11438,7 +11433,7 @@
         <v>17</v>
       </c>
       <c r="F55" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G55" t="s">
         <v>18</v>
@@ -11446,10 +11441,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C56" t="s">
         <v>58</v>
@@ -11461,7 +11456,7 @@
         <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G56" t="s">
         <v>27</v>
@@ -11477,14 +11472,14 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
-        <v>156</v>
+      <c r="A57" t="s">
+        <v>59</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D57">
         <v>0.54144160562658517</v>
@@ -11509,14 +11504,14 @@
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>156</v>
+      <c r="A58" t="s">
+        <v>59</v>
       </c>
       <c r="B58" t="s">
         <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>0.35853651380453599</v>
@@ -11545,7 +11540,7 @@
         <v>2</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
@@ -11553,7 +11548,7 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
@@ -11582,10 +11577,10 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
@@ -11636,10 +11631,10 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C68" t="s">
         <v>58</v>
@@ -11651,7 +11646,7 @@
         <v>17</v>
       </c>
       <c r="F68" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s">
         <v>18</v>
@@ -11659,10 +11654,10 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C69" t="s">
         <v>58</v>
@@ -11674,7 +11669,7 @@
         <v>17</v>
       </c>
       <c r="F69" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s">
         <v>27</v>
@@ -11761,10 +11756,10 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
         <v>58</v>
@@ -11776,7 +11771,7 @@
         <v>17</v>
       </c>
       <c r="F72" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G72" t="s">
         <v>27</v>
@@ -11799,7 +11794,7 @@
         <v>2</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
@@ -11807,7 +11802,7 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
@@ -11836,10 +11831,10 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
@@ -11890,10 +11885,10 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" t="s">
         <v>103</v>
-      </c>
-      <c r="B82" t="s">
-        <v>101</v>
       </c>
       <c r="C82" t="s">
         <v>58</v>
@@ -11905,7 +11900,7 @@
         <v>17</v>
       </c>
       <c r="F82" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G82" t="s">
         <v>18</v>
@@ -11913,10 +11908,10 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C83" t="s">
         <v>58</v>
@@ -11928,7 +11923,7 @@
         <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G83" t="s">
         <v>27</v>
@@ -11947,14 +11942,14 @@
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
-        <v>156</v>
+      <c r="A84" t="s">
+        <v>59</v>
       </c>
       <c r="B84" t="s">
         <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D84">
         <v>9.4726998574516978E-4</v>
@@ -11980,10 +11975,10 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C85" t="s">
         <v>58</v>
@@ -11995,7 +11990,7 @@
         <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G85" t="s">
         <v>27</v>
@@ -12047,10 +12042,10 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C87" t="s">
         <v>58</v>
@@ -12062,7 +12057,7 @@
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G87" t="s">
         <v>27</v>
@@ -12120,7 +12115,7 @@
         <v>2</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
@@ -12128,7 +12123,7 @@
         <v>3</v>
       </c>
       <c r="B91" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
@@ -12157,10 +12152,10 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B95" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
@@ -12211,10 +12206,10 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B98" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C98" t="s">
         <v>58</v>
@@ -12226,7 +12221,7 @@
         <v>17</v>
       </c>
       <c r="F98" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G98" t="s">
         <v>18</v>
@@ -12234,10 +12229,10 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
         <v>103</v>
-      </c>
-      <c r="B99" t="s">
-        <v>101</v>
       </c>
       <c r="C99" t="s">
         <v>58</v>
@@ -12249,7 +12244,7 @@
         <v>17</v>
       </c>
       <c r="F99" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G99" t="s">
         <v>27</v>
@@ -12268,14 +12263,14 @@
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A100" s="6" t="s">
-        <v>156</v>
+      <c r="A100" t="s">
+        <v>59</v>
       </c>
       <c r="B100" t="s">
         <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D100">
         <v>2.7228712509339933E-2</v>
@@ -12301,10 +12296,10 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C101" t="s">
         <v>58</v>
@@ -12316,7 +12311,7 @@
         <v>17</v>
       </c>
       <c r="F101" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G101" t="s">
         <v>27</v>
@@ -12367,14 +12362,14 @@
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A103" s="6" t="s">
-        <v>156</v>
+      <c r="A103" t="s">
+        <v>59</v>
       </c>
       <c r="B103" t="s">
         <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D103">
         <v>3.5000000000000001E-3</v>
@@ -12431,14 +12426,14 @@
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A105" s="6" t="s">
-        <v>156</v>
+      <c r="A105" t="s">
+        <v>59</v>
       </c>
       <c r="B105" t="s">
         <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D105">
         <v>0.3</v>
@@ -12482,7 +12477,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -12490,7 +12485,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -12519,10 +12514,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -12573,10 +12568,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
@@ -12588,7 +12583,7 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
@@ -12596,10 +12591,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -12620,10 +12615,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
         <v>54</v>
@@ -12644,10 +12639,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
         <v>54</v>
@@ -12668,10 +12663,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
         <v>54</v>
@@ -12692,10 +12687,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -12716,10 +12711,10 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -12731,7 +12726,7 @@
         <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
@@ -12769,10 +12764,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
         <v>45</v>
@@ -12785,7 +12780,7 @@
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
         <v>27</v>
@@ -12793,10 +12788,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
         <v>45</v>
@@ -12809,7 +12804,7 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G18" t="s">
         <v>27</v>
@@ -12832,7 +12827,7 @@
         <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
@@ -12840,7 +12835,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D20">
         <f>0.1/1000</f>
@@ -12856,12 +12851,12 @@
         <v>21</v>
       </c>
       <c r="H20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D21">
         <f>0.05/1000</f>
@@ -12877,7 +12872,7 @@
         <v>21</v>
       </c>
       <c r="H21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
